--- a/outputs/01a1629b-860b-7210-8c74-be734bc4de0b/Portfolio-Content-Editor.xlsx
+++ b/outputs/01a1629b-860b-7210-8c74-be734bc4de0b/Portfolio-Content-Editor.xlsx
@@ -5479,7 +5479,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Open to junior Java backend and backend developer roles</t>
+          <t>Open to Java backend developer roles</t>
         </is>
       </c>
     </row>

--- a/outputs/01a1629b-860b-7210-8c74-be734bc4de0b/Portfolio-Content-Editor.xlsx
+++ b/outputs/01a1629b-860b-7210-8c74-be734bc4de0b/Portfolio-Content-Editor.xlsx
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/problem-solving-basic.png</t>
+          <t>../assets/images/certificates/problem-solving-basic.svg</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/sql-basic.png</t>
+          <t>../assets/images/certificates/sql-basic.svg</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/sql-intermediate.png</t>
+          <t>../assets/images/certificates/sql-intermediate.svg</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/javascript-basic.png</t>
+          <t>../assets/images/certificates/javascript-basic.svg</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/sql-advanced.png</t>
+          <t>../assets/images/certificates/sql-advanced.svg</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/problem-solving-intermediate.png</t>
+          <t>../assets/images/certificates/problem-solving-intermediate.svg</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/java-basic.png</t>
+          <t>../assets/images/certificates/java-basic.svg</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/react-basic.png</t>
+          <t>../assets/images/certificates/react-basic.svg</t>
         </is>
       </c>
     </row>

--- a/outputs/01a1629b-860b-7210-8c74-be734bc4de0b/Portfolio-Content-Editor.xlsx
+++ b/outputs/01a1629b-860b-7210-8c74-be734bc4de0b/Portfolio-Content-Editor.xlsx
@@ -1031,6 +1031,16 @@
 JUnit</t>
         </is>
       </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/commerce-core</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/commerce-core</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1096,6 +1106,16 @@
 JUnit</t>
         </is>
       </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/event-flow</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/event-flow</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1161,6 +1181,16 @@
 JUnit</t>
         </is>
       </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/stockroom</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/stockroom</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1226,6 +1256,16 @@
 AWS RDS</t>
         </is>
       </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/shipshape</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/shipshape</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1291,6 +1331,16 @@
 Docker</t>
         </is>
       </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/quickcache</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/quickcache</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1356,6 +1406,16 @@
 JUnit</t>
         </is>
       </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/securegate</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/securegate</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1423,6 +1483,16 @@
       <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Back-End Web Development</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/tvamev-sahayak</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/tvamev-sahayak</t>
         </is>
       </c>
     </row>
@@ -1496,6 +1566,16 @@
           <t>Python</t>
         </is>
       </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/youtube-playlist-downloader</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/youtube-playlist-downloader</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1567,6 +1647,16 @@
           <t>Python</t>
         </is>
       </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/awareness-of-waste-recycling</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/awareness-of-waste-recycling</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1636,6 +1726,16 @@
       <c r="O11" s="4" t="inlineStr">
         <is>
           <t>Python</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/automatic-files-distributing-application</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/automatic-files-distributing-application</t>
         </is>
       </c>
     </row>
